--- a/tool/kintone-resourse-generator/template/custom/クラススペース_L01.xlsx
+++ b/tool/kintone-resourse-generator/template/custom/クラススペース_L01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\template\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AA445D-E52D-4900-A383-368B40C47ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98C7E4F-A755-4419-AC9F-7DD015274F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="space-settings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>管理者</t>
   </si>
@@ -102,10 +102,6 @@
   </si>
   <si>
     <t>ファイル書き出し</t>
-  </si>
-  <si>
-    <t>ユーザ</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>スペース名</t>
@@ -510,7 +506,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>15</v>
@@ -527,7 +523,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -814,25 +810,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
+      <c r="C4" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
